--- a/cognite/neat/examples/github-test-file.xlsx
+++ b/cognite/neat/examples/github-test-file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleksandrslivincovs/DevProject/Cognite/projects/neat/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF52A0FC-33F0-ED40-9A15-A1684E93009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780A2037-FB8C-C248-8EE6-F4304C2CDDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33640" yWindow="4620" windowWidth="35560" windowHeight="23060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="152">
   <si>
     <t>tnt</t>
   </si>
@@ -784,9 +784,6 @@
   </si>
   <si>
     <t>rootNode</t>
-  </si>
-  <si>
-    <t>Class2</t>
   </si>
 </sst>
 </file>
@@ -27362,7 +27359,7 @@
     </row>
     <row r="2" spans="1:20" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>58</v>
